--- a/FBStats25-26.xlsx
+++ b/FBStats25-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johntran/VSCode/VSCode for ACM/mpacmphase2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C294B24C-4ECB-7B4A-86C1-9AD016EC9724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248A78DE-9AE4-EE40-B587-B8CC6626FB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17100" xr2:uid="{802A0F31-8C0E-1546-A7F6-97F3B02C124B}"/>
   </bookViews>
@@ -47,127 +47,127 @@
     <t>Position</t>
   </si>
   <si>
-    <t>Goals</t>
-  </si>
-  <si>
-    <t>Assists</t>
-  </si>
-  <si>
-    <t>PassesPerGame</t>
-  </si>
-  <si>
-    <t>PassAccuracy</t>
-  </si>
-  <si>
-    <t>Fouls</t>
-  </si>
-  <si>
-    <t>SucessfulTackles</t>
+    <t>Lamine Yamal</t>
+  </si>
+  <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>Attacker</t>
+  </si>
+  <si>
+    <t>Pedri</t>
+  </si>
+  <si>
+    <t>Robert Lewandowski</t>
+  </si>
+  <si>
+    <t>Joan García</t>
+  </si>
+  <si>
+    <t>Wojciech Szczęsny</t>
+  </si>
+  <si>
+    <t>Ronald Araújo</t>
+  </si>
+  <si>
+    <t>Pau Cubarsí</t>
+  </si>
+  <si>
+    <t>Jules Koundé</t>
+  </si>
+  <si>
+    <t>Alejandro Balde</t>
+  </si>
+  <si>
+    <t>João Cancelo</t>
+  </si>
+  <si>
+    <t>Eric García</t>
+  </si>
+  <si>
+    <t>Gavi</t>
+  </si>
+  <si>
+    <t>Frenkie de Jong</t>
+  </si>
+  <si>
+    <t>Dani Olmo</t>
+  </si>
+  <si>
+    <t>Fermín López</t>
+  </si>
+  <si>
+    <t>Marc Casadó</t>
+  </si>
+  <si>
+    <t>Raphinha</t>
+  </si>
+  <si>
+    <t>Ferran Torres</t>
+  </si>
+  <si>
+    <t>Marcus Rashford</t>
+  </si>
+  <si>
+    <t>Roony Bardghji</t>
+  </si>
+  <si>
+    <t>Goalkeeper</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Midfielder</t>
+  </si>
+  <si>
+    <t>Gerard Martín</t>
+  </si>
+  <si>
+    <t>Andreas Christensen</t>
+  </si>
+  <si>
+    <t>Marc Bernal</t>
+  </si>
+  <si>
+    <t>GamesPlayed</t>
+  </si>
+  <si>
+    <t>ShotsPer90</t>
+  </si>
+  <si>
+    <t>ShotsOnTargetPer90</t>
+  </si>
+  <si>
+    <t>SavesPer90</t>
+  </si>
+  <si>
+    <t>GoalsPer90</t>
+  </si>
+  <si>
+    <t>AssistsPer90</t>
+  </si>
+  <si>
+    <t>PassesPer90</t>
+  </si>
+  <si>
+    <t>PassAccuracyPer90</t>
+  </si>
+  <si>
+    <t>FoulsPer90</t>
+  </si>
+  <si>
+    <t>SucessfulTacklesPer90</t>
+  </si>
+  <si>
+    <t>CleanSheetsPer90</t>
+  </si>
+  <si>
+    <t>RedCards</t>
   </si>
   <si>
     <t>YellowCards</t>
-  </si>
-  <si>
-    <t>RedCards</t>
-  </si>
-  <si>
-    <t>Saves</t>
-  </si>
-  <si>
-    <t>CleanSheets</t>
-  </si>
-  <si>
-    <t>Lamine Yamal</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
-    <t>Attacker</t>
-  </si>
-  <si>
-    <t>Pedri</t>
-  </si>
-  <si>
-    <t>Robert Lewandowski</t>
-  </si>
-  <si>
-    <t>Joan García</t>
-  </si>
-  <si>
-    <t>Wojciech Szczęsny</t>
-  </si>
-  <si>
-    <t>Ronald Araújo</t>
-  </si>
-  <si>
-    <t>Pau Cubarsí</t>
-  </si>
-  <si>
-    <t>Jules Koundé</t>
-  </si>
-  <si>
-    <t>Alejandro Balde</t>
-  </si>
-  <si>
-    <t>João Cancelo</t>
-  </si>
-  <si>
-    <t>Eric García</t>
-  </si>
-  <si>
-    <t>Gavi</t>
-  </si>
-  <si>
-    <t>Frenkie de Jong</t>
-  </si>
-  <si>
-    <t>Dani Olmo</t>
-  </si>
-  <si>
-    <t>Fermín López</t>
-  </si>
-  <si>
-    <t>Marc Casadó</t>
-  </si>
-  <si>
-    <t>Raphinha</t>
-  </si>
-  <si>
-    <t>Ferran Torres</t>
-  </si>
-  <si>
-    <t>Marcus Rashford</t>
-  </si>
-  <si>
-    <t>Roony Bardghji</t>
-  </si>
-  <si>
-    <t>Goalkeeper</t>
-  </si>
-  <si>
-    <t>Defender</t>
-  </si>
-  <si>
-    <t>Midfielder</t>
-  </si>
-  <si>
-    <t>Gerard Martín</t>
-  </si>
-  <si>
-    <t>Andreas Christensen</t>
-  </si>
-  <si>
-    <t>Marc Bernal</t>
-  </si>
-  <si>
-    <t>GamesPlayed</t>
-  </si>
-  <si>
-    <t>ShotsPerGame</t>
-  </si>
-  <si>
-    <t>ShotsOnTarget</t>
   </si>
 </sst>
 </file>
@@ -547,17 +547,17 @@
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12.1640625" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" customWidth="1"/>
-    <col min="15" max="15" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -571,476 +571,296 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2">
-        <v>37</v>
-      </c>
-      <c r="O2">
-        <v>99</v>
-      </c>
-      <c r="P2">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="O3">
-        <v>27</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5">
-        <v>41</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6">
-        <v>41</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="M9">
-        <v>8</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10">
-        <v>17</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11">
-        <v>43</v>
-      </c>
-      <c r="M11">
-        <v>4</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12">
-        <v>34</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14">
-        <v>31</v>
-      </c>
-      <c r="H14">
-        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15">
-        <v>39</v>
-      </c>
-      <c r="H15">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16">
-        <v>40</v>
-      </c>
-      <c r="H16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17">
-        <v>28</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18">
-        <v>29</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19">
-        <v>38</v>
-      </c>
-      <c r="E19">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20">
-        <v>41</v>
-      </c>
-      <c r="E20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21">
-        <v>31</v>
-      </c>
-      <c r="E21">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22">
-        <v>41</v>
-      </c>
-      <c r="E22">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23">
-        <v>40</v>
-      </c>
-      <c r="E23">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24">
-        <v>22</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
